--- a/docagent_clean_mvp/sample_data/raw_excels/NIST_SetA.xlsx
+++ b/docagent_clean_mvp/sample_data/raw_excels/NIST_SetA.xlsx
@@ -714,7 +714,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Endpoint devices are protected by centrally managed anti-malware with automatic signature updates.</t>
+          <t>Standard Protect function control mandates that endpoint devices are protected by centrally managed anti-malware with automatic signature updates. [NIST-009]</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -724,7 +724,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Compliant - EDR coverage 100% of managed endpoints</t>
+          <t>Compliant - last reviewed this cycle</t>
         </is>
       </c>
     </row>
